--- a/docs/学習メモ.xlsx
+++ b/docs/学習メモ.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="649">
   <si>
     <t>STEP1 importを書く</t>
   </si>
@@ -2735,6 +2735,51 @@
   </si>
   <si>
     <t>そこから一緒にレビューしながら、実務のコードレビューのように進めていきましょう。</t>
+  </si>
+  <si>
+    <t>┌────────────────────┐</t>
+  </si>
+  <si>
+    <t>│こんにちは          │</t>
+  </si>
+  <si>
+    <t>└────────────────────┘</t>
+  </si>
+  <si>
+    <t>と入力できますが、</t>
+  </si>
+  <si>
+    <t>Flutterは</t>
+  </si>
+  <si>
+    <t>「何が入力されたか」</t>
+  </si>
+  <si>
+    <t>を知りません。</t>
+  </si>
+  <si>
+    <t>そこで登場するのが</t>
+  </si>
+  <si>
+    <t>TextEditingController</t>
+  </si>
+  <si>
+    <t>イメージは</t>
+  </si>
+  <si>
+    <t>TextField</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     │</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     ▼</t>
+  </si>
+  <si>
+    <t>"こんばんは"</t>
+  </si>
+  <si>
+    <t>入力した文字を保存してくれる箱です。</t>
   </si>
 </sst>
 </file>
@@ -7667,6 +7712,604 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>350520</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>251460</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>304800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形吹き出し 1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6446520" y="17343120"/>
+          <a:ext cx="4777740" cy="4251960"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -79366"/>
+            <a:gd name="adj2" fmla="val -25453"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>① _messages </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>の下へ追加</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>現在は</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>late List&lt;Message&gt; _messages;</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>があります。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>その下へ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>final TextEditingController _controller = TextEditingController();</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>を追加します。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>すると</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>late List&lt;Message&gt; _messages;</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>final TextEditingController _controller = TextEditingController();</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>になります。</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>289560</xdr:colOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>464820</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="角丸四角形吹き出し 12"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10652760" y="18051780"/>
+          <a:ext cx="2613660" cy="4716780"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -61184"/>
+            <a:gd name="adj2" fmla="val -34772"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>② TextField</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>を探す</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>今は</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>TextField(</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>  decoration: ...</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>ですよね。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>これを</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>TextField(</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>  controller: _controller,</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>  decoration: const InputDecoration(</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>    hintText: "</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>メッセージを入力</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>",</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>    border: OutlineInputBorder(),</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>  ),</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>に変更します。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>追加するのはこの</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>1</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>行だけです。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>controller: _controller,</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>480060</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="角丸四角形吹き出し 14"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13106400" y="18112740"/>
+          <a:ext cx="2613660" cy="4777740"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -61184"/>
+            <a:gd name="adj2" fmla="val -34772"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>③ 動きのイメージ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>例えば、</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>こんばんは</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>と入力すると</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>_controller.text</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>の中には、</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>こんばんは</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>が入ります。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>つまり後で</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>print(_controller.text);</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>と書けば</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>こんばんは</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>が取得できます。</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -10269,7 +10912,782 @@
   <controls>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3104" r:id="rId3" name="Control 32">
+        <control shapeId="3073" r:id="rId3" name="Control 1">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>13</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>14</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3073" r:id="rId3" name="Control 1"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3074" r:id="rId5" name="Control 2">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>15</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>16</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3074" r:id="rId5" name="Control 2"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3075" r:id="rId6" name="Control 3">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>17</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>18</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3075" r:id="rId6" name="Control 3"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3076" r:id="rId7" name="Control 4">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>19</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>20</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3076" r:id="rId7" name="Control 4"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3077" r:id="rId8" name="Control 5">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>21</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>22</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3077" r:id="rId8" name="Control 5"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3078" r:id="rId9" name="Control 6">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>23</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>24</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3078" r:id="rId9" name="Control 6"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3079" r:id="rId10" name="Control 7">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>53</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>54</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3079" r:id="rId10" name="Control 7"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3080" r:id="rId11" name="Control 8">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>55</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>56</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3080" r:id="rId11" name="Control 8"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3081" r:id="rId12" name="Control 9">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>57</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>58</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3081" r:id="rId12" name="Control 9"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3082" r:id="rId13" name="Control 10">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>59</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>60</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3082" r:id="rId13" name="Control 10"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3083" r:id="rId14" name="Control 11">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>61</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>62</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3083" r:id="rId14" name="Control 11"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3084" r:id="rId15" name="Control 12">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>92</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>93</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3084" r:id="rId15" name="Control 12"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3085" r:id="rId16" name="Control 13">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>94</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>95</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3085" r:id="rId16" name="Control 13"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3086" r:id="rId17" name="Control 14">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>96</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>97</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3086" r:id="rId17" name="Control 14"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3087" r:id="rId18" name="Control 15">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>98</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>99</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3087" r:id="rId18" name="Control 15"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3088" r:id="rId19" name="Control 16">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>110</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>111</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3088" r:id="rId19" name="Control 16"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3089" r:id="rId20" name="Control 17">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>112</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>113</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3089" r:id="rId20" name="Control 17"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3090" r:id="rId21" name="Control 18">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>114</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>115</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3090" r:id="rId21" name="Control 18"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3091" r:id="rId22" name="Control 19">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>116</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>117</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3091" r:id="rId22" name="Control 19"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3092" r:id="rId23" name="Control 20">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>118</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>119</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3092" r:id="rId23" name="Control 20"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3093" r:id="rId24" name="Control 21">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>120</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>121</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3093" r:id="rId24" name="Control 21"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3094" r:id="rId25" name="Control 22">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>132</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>133</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3094" r:id="rId25" name="Control 22"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3095" r:id="rId26" name="Control 23">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>134</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>135</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3095" r:id="rId26" name="Control 23"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3096" r:id="rId27" name="Control 24">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>136</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>137</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3096" r:id="rId27" name="Control 24"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3097" r:id="rId28" name="Control 25">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>138</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>139</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3097" r:id="rId28" name="Control 25"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3098" r:id="rId29" name="Control 26">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>140</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>141</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3098" r:id="rId29" name="Control 26"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3099" r:id="rId30" name="Control 27">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>142</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>143</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3099" r:id="rId30" name="Control 27"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3100" r:id="rId31" name="Control 28">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>150</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>151</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3100" r:id="rId31" name="Control 28"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3101" r:id="rId32" name="Control 29">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>152</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>153</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3101" r:id="rId32" name="Control 29"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3102" r:id="rId33" name="Control 30">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>154</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>155</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3102" r:id="rId33" name="Control 30"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3103" r:id="rId34" name="Control 31">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>156</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>157</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3103" r:id="rId34" name="Control 31"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3104" r:id="rId35" name="Control 32">
           <controlPr defaultSize="0" r:id="rId4">
             <anchor moveWithCells="1">
               <from>
@@ -10289,782 +11707,7 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3104" r:id="rId3" name="Control 32"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3103" r:id="rId5" name="Control 31">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>156</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>157</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3103" r:id="rId5" name="Control 31"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3102" r:id="rId6" name="Control 30">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>154</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>155</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3102" r:id="rId6" name="Control 30"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3101" r:id="rId7" name="Control 29">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>152</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>153</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3101" r:id="rId7" name="Control 29"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3100" r:id="rId8" name="Control 28">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>150</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>151</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3100" r:id="rId8" name="Control 28"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3099" r:id="rId9" name="Control 27">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>142</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>143</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3099" r:id="rId9" name="Control 27"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3098" r:id="rId10" name="Control 26">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>140</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>141</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3098" r:id="rId10" name="Control 26"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3097" r:id="rId11" name="Control 25">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>138</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>139</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3097" r:id="rId11" name="Control 25"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3096" r:id="rId12" name="Control 24">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>136</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>137</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3096" r:id="rId12" name="Control 24"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3095" r:id="rId13" name="Control 23">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>134</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>135</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3095" r:id="rId13" name="Control 23"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3094" r:id="rId14" name="Control 22">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>132</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>133</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3094" r:id="rId14" name="Control 22"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3093" r:id="rId15" name="Control 21">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>120</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>121</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3093" r:id="rId15" name="Control 21"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3092" r:id="rId16" name="Control 20">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>118</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>119</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3092" r:id="rId16" name="Control 20"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3091" r:id="rId17" name="Control 19">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>116</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>117</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3091" r:id="rId17" name="Control 19"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3090" r:id="rId18" name="Control 18">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>114</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>115</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3090" r:id="rId18" name="Control 18"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3089" r:id="rId19" name="Control 17">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>112</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>113</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3089" r:id="rId19" name="Control 17"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3088" r:id="rId20" name="Control 16">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>110</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>111</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3088" r:id="rId20" name="Control 16"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3087" r:id="rId21" name="Control 15">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>98</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>99</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3087" r:id="rId21" name="Control 15"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3086" r:id="rId22" name="Control 14">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>96</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>97</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3086" r:id="rId22" name="Control 14"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3085" r:id="rId23" name="Control 13">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>94</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>95</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3085" r:id="rId23" name="Control 13"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3084" r:id="rId24" name="Control 12">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>92</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>93</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3084" r:id="rId24" name="Control 12"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3083" r:id="rId25" name="Control 11">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>61</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>62</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3083" r:id="rId25" name="Control 11"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3082" r:id="rId26" name="Control 10">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>59</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>60</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3082" r:id="rId26" name="Control 10"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3081" r:id="rId27" name="Control 9">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>57</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>58</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3081" r:id="rId27" name="Control 9"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3080" r:id="rId28" name="Control 8">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>55</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>56</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3080" r:id="rId28" name="Control 8"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3079" r:id="rId29" name="Control 7">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>53</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>54</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3079" r:id="rId29" name="Control 7"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3078" r:id="rId30" name="Control 6">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>23</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>24</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3078" r:id="rId30" name="Control 6"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3077" r:id="rId31" name="Control 5">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>21</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>22</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3077" r:id="rId31" name="Control 5"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3076" r:id="rId32" name="Control 4">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>19</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>20</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3076" r:id="rId32" name="Control 4"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3075" r:id="rId33" name="Control 3">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>17</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>18</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3075" r:id="rId33" name="Control 3"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3074" r:id="rId34" name="Control 2">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>15</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>16</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3074" r:id="rId34" name="Control 2"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3073" r:id="rId35" name="Control 1">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>13</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>14</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3073" r:id="rId35" name="Control 1"/>
+        <control shapeId="3104" r:id="rId35" name="Control 32"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </controls>
@@ -12941,7 +13584,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:B236"/>
+  <dimension ref="B2:G255"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="8.88671875" style="2"/>
@@ -13212,440 +13855,536 @@
         <v>590</v>
       </c>
     </row>
-    <row r="99" spans="2:2" ht="28.2" x14ac:dyDescent="0.2">
-      <c r="B99" s="1" t="s">
+    <row r="97" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B97" s="2" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="98" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B98" s="3"/>
+      <c r="G98" s="2" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="99" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B99" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="G99" s="3"/>
+    </row>
+    <row r="100" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B100" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="G100" s="4" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="101" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B101" s="4" t="s">
+        <v>636</v>
+      </c>
+      <c r="G101" s="4" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="102" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="G102" s="4" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="103" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B103" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="G103" s="4" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="104" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="G104" s="4" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="105" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B105" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="G105" s="4" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="106" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B106" s="7"/>
+      <c r="G106" s="4" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="107" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B107" s="7" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="108" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G108" s="2" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="109" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B109" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="111" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B111" s="2" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="113" spans="2:2" ht="21" x14ac:dyDescent="0.2">
+      <c r="B113" s="6" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B115" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="118" spans="2:2" ht="28.2" x14ac:dyDescent="0.2">
+      <c r="B118" s="1" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="101" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B101" s="4" t="s">
+    <row r="120" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B120" s="4" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="102" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B102" s="4" t="s">
+    <row r="121" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B121" s="4" t="s">
         <v>593</v>
-      </c>
-    </row>
-    <row r="103" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B103" s="4" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="104" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B104" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="105" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B105" s="3"/>
-    </row>
-    <row r="106" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B106" s="4" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="107" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B107" s="4" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="108" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B108" s="4" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="109" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B109" s="4" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="110" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B110" s="4" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="111" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B111" s="4" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="112" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B112" s="4" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="113" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B113" s="4" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="114" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B114" s="4" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="115" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B115" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="116" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B116" s="3"/>
-    </row>
-    <row r="117" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B117" s="4" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="118" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B118" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="120" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B120" s="2" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="122" spans="2:2" ht="15" x14ac:dyDescent="0.2">
       <c r="B122" s="4" t="s">
-        <v>604</v>
+        <v>594</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B123" s="4" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="124" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B124" s="2" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="125" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B125" s="7"/>
-    </row>
-    <row r="126" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B126" s="7" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="128" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B128" s="2" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="132" spans="2:2" ht="28.2" x14ac:dyDescent="0.2">
-      <c r="B132" s="1" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="134" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B134" s="2" t="s">
-        <v>568</v>
-      </c>
+      <c r="B124" s="3"/>
+    </row>
+    <row r="125" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B125" s="4" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="126" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B126" s="4" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="127" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B127" s="4" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="128" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B128" s="4" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="129" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B129" s="4" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="130" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B130" s="4" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="131" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B131" s="4" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="132" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B132" s="4" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="133" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B133" s="4" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="134" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B134" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B135" s="3"/>
     </row>
     <row r="136" spans="2:2" ht="15" x14ac:dyDescent="0.2">
       <c r="B136" s="4" t="s">
-        <v>422</v>
+        <v>602</v>
       </c>
     </row>
     <row r="137" spans="2:2" ht="15" x14ac:dyDescent="0.2">
       <c r="B137" s="4" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="138" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B138" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="140" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B140" s="2" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="142" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B142" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="144" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B144" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B139" s="2" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="141" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B141" s="4" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="143" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B143" s="2" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="144" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B144" s="7"/>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B145" s="7" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B147" s="2" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="151" spans="2:2" ht="28.2" x14ac:dyDescent="0.2">
+      <c r="B151" s="1" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="153" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B153" s="2" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="155" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B155" s="4" t="s">
         <v>422</v>
-      </c>
-    </row>
-    <row r="145" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B145" s="4" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="146" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B146" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="148" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B148" s="2" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="152" spans="2:2" ht="28.2" x14ac:dyDescent="0.2">
-      <c r="B152" s="1" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B154" s="2" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="156" spans="2:2" ht="15" x14ac:dyDescent="0.2">
       <c r="B156" s="4" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B158" s="2" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B160" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="157" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B157" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="159" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B159" s="2" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B161" s="2" t="s">
         <v>118</v>
-      </c>
-    </row>
-    <row r="162" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B162" s="4" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="163" spans="2:2" ht="15" x14ac:dyDescent="0.2">
       <c r="B163" s="4" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="164" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B164" s="4" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="165" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B165" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B167" s="2" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="171" spans="2:2" ht="28.2" x14ac:dyDescent="0.2">
+      <c r="B171" s="1" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B173" s="2" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="175" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B175" s="4" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="177" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B177" s="2" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="179" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B179" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="181" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B181" s="4" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="182" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B182" s="4" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B165" s="2" t="s">
+    <row r="184" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B184" s="2" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="169" spans="2:2" ht="28.2" x14ac:dyDescent="0.2">
-      <c r="B169" s="1" t="s">
+    <row r="188" spans="2:2" ht="28.2" x14ac:dyDescent="0.2">
+      <c r="B188" s="1" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B171" s="2" t="s">
+    <row r="190" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B190" s="2" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="173" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B173" s="4" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="174" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B174" s="4" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B176" s="2" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="178" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B178" s="4" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="180" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B180" s="2" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="184" spans="2:2" ht="28.2" x14ac:dyDescent="0.2">
-      <c r="B184" s="1" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="186" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B186" s="2" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="188" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B188" s="4" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="189" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B189" s="3"/>
-    </row>
-    <row r="190" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B190" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B191" s="3"/>
     </row>
     <row r="192" spans="2:2" ht="15" x14ac:dyDescent="0.2">
       <c r="B192" s="4" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="193" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B193" s="4" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B195" s="2" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B197" s="4" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="199" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B199" s="2" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="203" spans="2:2" ht="28.2" x14ac:dyDescent="0.2">
+      <c r="B203" s="1" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="205" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B205" s="2" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="207" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B207" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="208" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B208" s="3"/>
+    </row>
+    <row r="209" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B209" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="210" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B210" s="3"/>
+    </row>
+    <row r="211" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B211" s="4" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B193" s="3"/>
-    </row>
-    <row r="194" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B194" s="4" t="s">
+    <row r="212" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B212" s="3"/>
+    </row>
+    <row r="213" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B213" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B195" s="3"/>
-    </row>
-    <row r="196" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B196" s="4" t="s">
+    <row r="214" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B214" s="3"/>
+    </row>
+    <row r="215" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B215" s="4" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B197" s="3"/>
-    </row>
-    <row r="198" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B198" s="4" t="s">
+    <row r="216" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B216" s="3"/>
+    </row>
+    <row r="217" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B217" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="199" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B199" s="3"/>
-    </row>
-    <row r="200" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B200" s="4" t="s">
+    <row r="218" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B218" s="3"/>
+    </row>
+    <row r="219" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B219" s="4" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="201" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B201" s="3"/>
-    </row>
-    <row r="202" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B202" s="4" t="s">
+    <row r="220" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B220" s="3"/>
+    </row>
+    <row r="221" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B221" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B203" s="3"/>
-    </row>
-    <row r="204" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B204" s="4" t="s">
+    <row r="222" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B222" s="3"/>
+    </row>
+    <row r="223" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B223" s="4" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="205" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B205" s="3"/>
-    </row>
-    <row r="206" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B206" s="4" t="s">
+    <row r="224" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B224" s="3"/>
+    </row>
+    <row r="225" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B225" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="207" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B207" s="3"/>
-    </row>
-    <row r="208" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B208" s="4" t="s">
+    <row r="226" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B226" s="3"/>
+    </row>
+    <row r="227" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B227" s="4" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="209" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B209" s="3"/>
-    </row>
-    <row r="210" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B210" s="4" t="s">
+    <row r="228" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B228" s="3"/>
+    </row>
+    <row r="229" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B229" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="211" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B211" s="3"/>
-    </row>
-    <row r="212" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B212" s="4" t="s">
+    <row r="230" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B230" s="3"/>
+    </row>
+    <row r="231" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B231" s="4" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="213" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B213" s="3"/>
-    </row>
-    <row r="214" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B214" s="4" t="s">
+    <row r="232" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B232" s="3"/>
+    </row>
+    <row r="233" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B233" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="215" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B215" s="3"/>
-    </row>
-    <row r="216" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B216" s="4" t="s">
+    <row r="234" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B234" s="3"/>
+    </row>
+    <row r="235" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B235" s="4" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="220" spans="2:2" ht="21" x14ac:dyDescent="0.2">
-      <c r="B220" s="6" t="s">
+    <row r="239" spans="2:2" ht="21" x14ac:dyDescent="0.2">
+      <c r="B239" s="6" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="222" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B222" s="2" t="s">
+    <row r="241" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B241" s="2" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="224" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B224" s="2" t="s">
+    <row r="243" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B243" s="2" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="225" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B225" s="7"/>
-    </row>
-    <row r="226" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B226" s="22" t="s">
+    <row r="244" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B244" s="7"/>
+    </row>
+    <row r="245" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B245" s="22" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="227" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B227" s="7"/>
-    </row>
-    <row r="228" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B228" s="22" t="s">
+    <row r="246" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B246" s="7"/>
+    </row>
+    <row r="247" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B247" s="22" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="229" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B229" s="7"/>
-    </row>
-    <row r="230" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B230" s="22" t="s">
+    <row r="248" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B248" s="7"/>
+    </row>
+    <row r="249" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B249" s="22" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="232" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B232" s="2" t="s">
+    <row r="251" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B251" s="2" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="234" spans="2:2" ht="15" x14ac:dyDescent="0.35">
-      <c r="B234" s="2" t="s">
+    <row r="253" spans="2:2" ht="15" x14ac:dyDescent="0.35">
+      <c r="B253" s="2" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="236" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B236" s="2" t="s">
+    <row r="255" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B255" s="2" t="s">
         <v>633</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/docs/学習メモ.xlsx
+++ b/docs/学習メモ.xlsx
@@ -8310,6 +8310,626 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>251460</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="角丸四角形吹き出し 15"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14881860" y="20040600"/>
+          <a:ext cx="2186940" cy="2125980"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -61184"/>
+            <a:gd name="adj2" fmla="val -34772"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" b="1"/>
+            <a:t>なぜ必要なの？</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>送信ボタンを押したとき、</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+        </a:p>
+        <a:p>
+          <a:pPr rtl="0"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>_controller.text</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>を読んで</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr rtl="0"/>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+        </a:p>
+        <a:p>
+          <a:pPr rtl="0"/>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>新しい</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>Message</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>を作る</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>という流れになります。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>601980</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>487680</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>274320</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="角丸四角形吹き出し 16"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17061180" y="20040600"/>
+          <a:ext cx="4152900" cy="1524000"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -61184"/>
+            <a:gd name="adj2" fmla="val -34772"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" b="1"/>
+            <a:t>今回の作業</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>追加するのはたった</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>2</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>か所です。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>①</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>final TextEditingController _controller = TextEditingController();</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>②</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>controller: _controller,</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>99060</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>243840</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="角丸四角形吹き出し 17"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20215860" y="17868900"/>
+          <a:ext cx="4411980" cy="2247900"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -72905"/>
+            <a:gd name="adj2" fmla="val -24990"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" b="1"/>
+            <a:t>💡 ワンポイント（実務でも大事）</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>TextEditingController </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>は使い終わったら解放する必要があります。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>今回は送信機能が完成したあとに、次のコードも追加します。</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>@override</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>void dispose() {</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>  _controller.dispose();</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>  super.dispose();</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>}</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>これはメモリリークを防ぐための</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>Flutter</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>のお作法です。</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>205740</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>205740</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>106680</xdr:colOff>
+      <xdr:row>122</xdr:row>
+      <xdr:rowOff>182880</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="角丸四角形吹き出し 18"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3253740" y="21496020"/>
+          <a:ext cx="4777740" cy="1074420"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -63098"/>
+            <a:gd name="adj2" fmla="val -19409"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>① build() </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>の前にメソッドを追加</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" b="1"/>
+            <a:t>dispose() </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" b="1"/>
+            <a:t>と </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" b="1"/>
+            <a:t>build() </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" b="1"/>
+            <a:t>の間</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>に、まず次のコードを追加してください。</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>void _sendMessage() {</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>}</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>205740</xdr:colOff>
+      <xdr:row>122</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>106680</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="角丸四角形吹き出し 19"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3253740" y="22562820"/>
+          <a:ext cx="4777740" cy="2301240"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -26734"/>
+            <a:gd name="adj2" fmla="val -60825"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>この </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>_sendMessage() </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>は何？</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>送信ボタン</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>   ↓</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>_sendMessage()</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>   ↓</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>メッセージを追加</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>名前の通り、という役割を持つメソッドです。今はまだ中身が空です。</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>次のステップで、この中に「</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>_controller.text</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>」を使って入力された文字を取得する処理を追加します。</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>まずは </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>_sendMessage() </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>を追加するだけで大丈夫です。</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -10912,7 +11532,782 @@
   <controls>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3073" r:id="rId3" name="Control 1">
+        <control shapeId="3104" r:id="rId3" name="Control 32">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>158</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>159</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3104" r:id="rId3" name="Control 32"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3103" r:id="rId5" name="Control 31">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>156</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>157</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3103" r:id="rId5" name="Control 31"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3102" r:id="rId6" name="Control 30">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>154</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>155</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3102" r:id="rId6" name="Control 30"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3101" r:id="rId7" name="Control 29">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>152</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>153</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3101" r:id="rId7" name="Control 29"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3100" r:id="rId8" name="Control 28">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>150</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>151</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3100" r:id="rId8" name="Control 28"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3099" r:id="rId9" name="Control 27">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>142</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>143</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3099" r:id="rId9" name="Control 27"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3098" r:id="rId10" name="Control 26">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>140</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>141</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3098" r:id="rId10" name="Control 26"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3097" r:id="rId11" name="Control 25">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>138</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>139</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3097" r:id="rId11" name="Control 25"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3096" r:id="rId12" name="Control 24">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>136</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>137</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3096" r:id="rId12" name="Control 24"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3095" r:id="rId13" name="Control 23">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>134</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>135</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3095" r:id="rId13" name="Control 23"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3094" r:id="rId14" name="Control 22">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>132</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>133</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3094" r:id="rId14" name="Control 22"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3093" r:id="rId15" name="Control 21">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>120</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>121</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3093" r:id="rId15" name="Control 21"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3092" r:id="rId16" name="Control 20">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>118</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>119</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3092" r:id="rId16" name="Control 20"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3091" r:id="rId17" name="Control 19">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>116</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>117</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3091" r:id="rId17" name="Control 19"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3090" r:id="rId18" name="Control 18">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>114</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>115</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3090" r:id="rId18" name="Control 18"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3089" r:id="rId19" name="Control 17">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>112</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>113</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3089" r:id="rId19" name="Control 17"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3088" r:id="rId20" name="Control 16">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>110</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>111</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3088" r:id="rId20" name="Control 16"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3087" r:id="rId21" name="Control 15">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>98</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>99</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3087" r:id="rId21" name="Control 15"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3086" r:id="rId22" name="Control 14">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>96</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>97</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3086" r:id="rId22" name="Control 14"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3085" r:id="rId23" name="Control 13">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>94</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>95</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3085" r:id="rId23" name="Control 13"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3084" r:id="rId24" name="Control 12">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>92</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>93</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3084" r:id="rId24" name="Control 12"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3083" r:id="rId25" name="Control 11">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>61</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>62</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3083" r:id="rId25" name="Control 11"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3082" r:id="rId26" name="Control 10">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>59</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>60</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3082" r:id="rId26" name="Control 10"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3081" r:id="rId27" name="Control 9">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>57</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>58</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3081" r:id="rId27" name="Control 9"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3080" r:id="rId28" name="Control 8">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>55</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>56</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3080" r:id="rId28" name="Control 8"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3079" r:id="rId29" name="Control 7">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>53</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>54</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3079" r:id="rId29" name="Control 7"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3078" r:id="rId30" name="Control 6">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>23</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>24</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3078" r:id="rId30" name="Control 6"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3077" r:id="rId31" name="Control 5">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>21</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>22</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3077" r:id="rId31" name="Control 5"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3076" r:id="rId32" name="Control 4">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>19</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>20</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3076" r:id="rId32" name="Control 4"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3075" r:id="rId33" name="Control 3">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>17</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>18</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3075" r:id="rId33" name="Control 3"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3074" r:id="rId34" name="Control 2">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>15</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>16</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3074" r:id="rId34" name="Control 2"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3073" r:id="rId35" name="Control 1">
           <controlPr defaultSize="0" r:id="rId4">
             <anchor moveWithCells="1">
               <from>
@@ -10932,782 +12327,7 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3073" r:id="rId3" name="Control 1"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3074" r:id="rId5" name="Control 2">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>15</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>16</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3074" r:id="rId5" name="Control 2"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3075" r:id="rId6" name="Control 3">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>17</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>18</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3075" r:id="rId6" name="Control 3"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3076" r:id="rId7" name="Control 4">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>19</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>20</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3076" r:id="rId7" name="Control 4"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3077" r:id="rId8" name="Control 5">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>21</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>22</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3077" r:id="rId8" name="Control 5"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3078" r:id="rId9" name="Control 6">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>23</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>24</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3078" r:id="rId9" name="Control 6"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3079" r:id="rId10" name="Control 7">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>53</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>54</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3079" r:id="rId10" name="Control 7"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3080" r:id="rId11" name="Control 8">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>55</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>56</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3080" r:id="rId11" name="Control 8"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3081" r:id="rId12" name="Control 9">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>57</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>58</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3081" r:id="rId12" name="Control 9"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3082" r:id="rId13" name="Control 10">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>59</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>60</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3082" r:id="rId13" name="Control 10"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3083" r:id="rId14" name="Control 11">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>61</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>62</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3083" r:id="rId14" name="Control 11"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3084" r:id="rId15" name="Control 12">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>92</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>93</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3084" r:id="rId15" name="Control 12"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3085" r:id="rId16" name="Control 13">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>94</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>95</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3085" r:id="rId16" name="Control 13"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3086" r:id="rId17" name="Control 14">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>96</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>97</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3086" r:id="rId17" name="Control 14"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3087" r:id="rId18" name="Control 15">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>98</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>99</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3087" r:id="rId18" name="Control 15"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3088" r:id="rId19" name="Control 16">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>110</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>111</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3088" r:id="rId19" name="Control 16"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3089" r:id="rId20" name="Control 17">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>112</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>113</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3089" r:id="rId20" name="Control 17"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3090" r:id="rId21" name="Control 18">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>114</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>115</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3090" r:id="rId21" name="Control 18"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3091" r:id="rId22" name="Control 19">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>116</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>117</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3091" r:id="rId22" name="Control 19"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3092" r:id="rId23" name="Control 20">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>118</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>119</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3092" r:id="rId23" name="Control 20"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3093" r:id="rId24" name="Control 21">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>120</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>121</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3093" r:id="rId24" name="Control 21"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3094" r:id="rId25" name="Control 22">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>132</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>133</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3094" r:id="rId25" name="Control 22"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3095" r:id="rId26" name="Control 23">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>134</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>135</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3095" r:id="rId26" name="Control 23"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3096" r:id="rId27" name="Control 24">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>136</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>137</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3096" r:id="rId27" name="Control 24"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3097" r:id="rId28" name="Control 25">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>138</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>139</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3097" r:id="rId28" name="Control 25"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3098" r:id="rId29" name="Control 26">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>140</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>141</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3098" r:id="rId29" name="Control 26"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3099" r:id="rId30" name="Control 27">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>142</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>143</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3099" r:id="rId30" name="Control 27"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3100" r:id="rId31" name="Control 28">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>150</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>151</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3100" r:id="rId31" name="Control 28"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3101" r:id="rId32" name="Control 29">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>152</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>153</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3101" r:id="rId32" name="Control 29"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3102" r:id="rId33" name="Control 30">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>154</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>155</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3102" r:id="rId33" name="Control 30"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3103" r:id="rId34" name="Control 31">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>156</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>157</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3103" r:id="rId34" name="Control 31"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3104" r:id="rId35" name="Control 32">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>158</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>159</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3104" r:id="rId35" name="Control 32"/>
+        <control shapeId="3073" r:id="rId35" name="Control 1"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </controls>

--- a/docs/学習メモ.xlsx
+++ b/docs/学習メモ.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="4"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="memo" sheetId="1" r:id="rId1"/>
@@ -8930,6 +8930,691 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>125</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>510540</xdr:colOff>
+      <xdr:row>131</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="角丸四角形吹き出し 24"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7924800" y="22936200"/>
+          <a:ext cx="4777740" cy="1188720"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -58951"/>
+            <a:gd name="adj2" fmla="val -57183"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" b="1"/>
+            <a:t>Step 6</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" b="1"/>
+            <a:t>：入力したメッセージを取得する</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>今作った </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>_sendMessage() </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>の中に、まず「入力欄に何が入っているか」を取得する処理を追加します。</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>↓のように変更してください。</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>void _sendMessage() { final text = _controller.text; }</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>106680</xdr:colOff>
+      <xdr:row>131</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>142</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="角丸四角形吹き出し 25"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8031480" y="24086820"/>
+          <a:ext cx="4777740" cy="2042160"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -18122"/>
+            <a:gd name="adj2" fmla="val -57231"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>次は </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" b="1"/>
+            <a:t>Step 7</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" b="1"/>
+            <a:t>：空のメッセージを送れないようにする</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t> です。</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>この </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" b="1"/>
+            <a:t>final text = _controller.text; </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" b="1"/>
+            <a:t>の次の行</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t> に、以下を追加してください。</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>if (text.trim().isEmpty) { return; }</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" b="1"/>
+            <a:t>何をしている？</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>例えば送信ボタンを押したとき、</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>"</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>こんにちは</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>" → </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>送信処理を続ける</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>"" → </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>何もしない</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>" " → </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>何もしない</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>という動きにするための処理です。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>502920</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>403860</xdr:colOff>
+      <xdr:row>142</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="角丸四角形吹き出し 26"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12694920" y="22776180"/>
+          <a:ext cx="4777740" cy="3413760"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -53051"/>
+            <a:gd name="adj2" fmla="val -26634"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>Step 8</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>：入力したメッセージを </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>_messages </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>に追加する</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>if </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>の下に、次の処理を追加します。</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>setState(() {</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>  _messages.add(</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>    Message(</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>      senderName: "</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>自分</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>",</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>      text: text,</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>      createdAt: DateTime.now(),</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>      isMine: true,</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>    ),</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>  );</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>});</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" b="1"/>
+            <a:t>今回やっていること</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>送信ボタンを押したら、</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>入力欄 → </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>text </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>に取得 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>→</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>Message</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>を作成 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>→</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>_messages </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>に追加 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>→</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>setState</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>で画面を更新</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>という流れになります。</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>45720</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>556260</xdr:colOff>
+      <xdr:row>137</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="角丸四角形吹き出し 27"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17114520" y="22745700"/>
+          <a:ext cx="4777740" cy="2537460"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -53051"/>
+            <a:gd name="adj2" fmla="val -26634"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>ElevatedButton(</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>  onPressed: () {</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>    // Sprint1</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>では未実装</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>},</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>  child: const Text("</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>送信</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>"),</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>),</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>途中だった上記に「</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP"/>
+            <a:t>_sendMessage();</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>」を追加する。</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>これで、</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" b="1"/>
+            <a:t>送信ボタンを押す → </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" b="1"/>
+            <a:t>_sendMessage() </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" b="1"/>
+            <a:t>が実行される</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>という状態になります。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -11532,19 +12217,19 @@
   <controls>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3104" r:id="rId3" name="Control 32">
+        <control shapeId="3073" r:id="rId3" name="Control 1">
           <controlPr defaultSize="0" r:id="rId4">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>158</xdr:row>
+                <xdr:row>13</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>159</xdr:row>
+                <xdr:row>14</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </to>
             </anchor>
@@ -11552,24 +12237,24 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3104" r:id="rId3" name="Control 32"/>
+        <control shapeId="3073" r:id="rId3" name="Control 1"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3103" r:id="rId5" name="Control 31">
-          <controlPr defaultSize="0" r:id="rId4">
+        <control shapeId="3074" r:id="rId5" name="Control 2">
+          <controlPr defaultSize="0" r:id="rId6">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>156</xdr:row>
+                <xdr:row>15</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>157</xdr:row>
+                <xdr:row>16</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </to>
             </anchor>
@@ -11577,24 +12262,24 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3103" r:id="rId5" name="Control 31"/>
+        <control shapeId="3074" r:id="rId5" name="Control 2"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3102" r:id="rId6" name="Control 30">
+        <control shapeId="3075" r:id="rId7" name="Control 3">
           <controlPr defaultSize="0" r:id="rId4">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>154</xdr:row>
+                <xdr:row>17</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>155</xdr:row>
+                <xdr:row>18</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </to>
             </anchor>
@@ -11602,24 +12287,24 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3102" r:id="rId6" name="Control 30"/>
+        <control shapeId="3075" r:id="rId7" name="Control 3"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3101" r:id="rId7" name="Control 29">
+        <control shapeId="3076" r:id="rId8" name="Control 4">
           <controlPr defaultSize="0" r:id="rId4">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>152</xdr:row>
+                <xdr:row>19</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>153</xdr:row>
+                <xdr:row>20</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </to>
             </anchor>
@@ -11627,24 +12312,24 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3101" r:id="rId7" name="Control 29"/>
+        <control shapeId="3076" r:id="rId8" name="Control 4"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3100" r:id="rId8" name="Control 28">
-          <controlPr defaultSize="0" r:id="rId4">
+        <control shapeId="3077" r:id="rId9" name="Control 5">
+          <controlPr defaultSize="0" r:id="rId6">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>150</xdr:row>
+                <xdr:row>21</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>151</xdr:row>
+                <xdr:row>22</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </to>
             </anchor>
@@ -11652,24 +12337,24 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3100" r:id="rId8" name="Control 28"/>
+        <control shapeId="3077" r:id="rId9" name="Control 5"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3099" r:id="rId9" name="Control 27">
-          <controlPr defaultSize="0" r:id="rId4">
+        <control shapeId="3078" r:id="rId10" name="Control 6">
+          <controlPr defaultSize="0" r:id="rId6">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>142</xdr:row>
+                <xdr:row>23</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>143</xdr:row>
+                <xdr:row>24</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </to>
             </anchor>
@@ -11677,24 +12362,24 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3099" r:id="rId9" name="Control 27"/>
+        <control shapeId="3078" r:id="rId10" name="Control 6"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3098" r:id="rId10" name="Control 26">
-          <controlPr defaultSize="0" r:id="rId4">
+        <control shapeId="3079" r:id="rId11" name="Control 7">
+          <controlPr defaultSize="0" r:id="rId6">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>140</xdr:row>
+                <xdr:row>53</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>141</xdr:row>
+                <xdr:row>54</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </to>
             </anchor>
@@ -11702,24 +12387,24 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3098" r:id="rId10" name="Control 26"/>
+        <control shapeId="3079" r:id="rId11" name="Control 7"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3097" r:id="rId11" name="Control 25">
-          <controlPr defaultSize="0" r:id="rId4">
+        <control shapeId="3080" r:id="rId12" name="Control 8">
+          <controlPr defaultSize="0" r:id="rId6">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>138</xdr:row>
+                <xdr:row>55</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>139</xdr:row>
+                <xdr:row>56</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </to>
             </anchor>
@@ -11727,24 +12412,24 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3097" r:id="rId11" name="Control 25"/>
+        <control shapeId="3080" r:id="rId12" name="Control 8"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3096" r:id="rId12" name="Control 24">
-          <controlPr defaultSize="0" r:id="rId4">
+        <control shapeId="3081" r:id="rId13" name="Control 9">
+          <controlPr defaultSize="0" r:id="rId6">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>136</xdr:row>
+                <xdr:row>57</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>137</xdr:row>
+                <xdr:row>58</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </to>
             </anchor>
@@ -11752,24 +12437,24 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3096" r:id="rId12" name="Control 24"/>
+        <control shapeId="3081" r:id="rId13" name="Control 9"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3095" r:id="rId13" name="Control 23">
-          <controlPr defaultSize="0" r:id="rId4">
+        <control shapeId="3082" r:id="rId14" name="Control 10">
+          <controlPr defaultSize="0" r:id="rId6">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>134</xdr:row>
+                <xdr:row>59</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>135</xdr:row>
+                <xdr:row>60</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </to>
             </anchor>
@@ -11777,24 +12462,24 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3095" r:id="rId13" name="Control 23"/>
+        <control shapeId="3082" r:id="rId14" name="Control 10"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3094" r:id="rId14" name="Control 22">
-          <controlPr defaultSize="0" r:id="rId4">
+        <control shapeId="3083" r:id="rId15" name="Control 11">
+          <controlPr defaultSize="0" r:id="rId6">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>132</xdr:row>
+                <xdr:row>61</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>133</xdr:row>
+                <xdr:row>62</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </to>
             </anchor>
@@ -11802,24 +12487,24 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3094" r:id="rId14" name="Control 22"/>
+        <control shapeId="3083" r:id="rId15" name="Control 11"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3093" r:id="rId15" name="Control 21">
-          <controlPr defaultSize="0" r:id="rId4">
+        <control shapeId="3084" r:id="rId16" name="Control 12">
+          <controlPr defaultSize="0" r:id="rId6">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>120</xdr:row>
+                <xdr:row>92</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>121</xdr:row>
+                <xdr:row>93</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </to>
             </anchor>
@@ -11827,24 +12512,24 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3093" r:id="rId15" name="Control 21"/>
+        <control shapeId="3084" r:id="rId16" name="Control 12"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3092" r:id="rId16" name="Control 20">
-          <controlPr defaultSize="0" r:id="rId4">
+        <control shapeId="3085" r:id="rId17" name="Control 13">
+          <controlPr defaultSize="0" r:id="rId6">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>118</xdr:row>
+                <xdr:row>94</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>119</xdr:row>
+                <xdr:row>95</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </to>
             </anchor>
@@ -11852,24 +12537,24 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3092" r:id="rId16" name="Control 20"/>
+        <control shapeId="3085" r:id="rId17" name="Control 13"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3091" r:id="rId17" name="Control 19">
-          <controlPr defaultSize="0" r:id="rId4">
+        <control shapeId="3086" r:id="rId18" name="Control 14">
+          <controlPr defaultSize="0" r:id="rId6">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>116</xdr:row>
+                <xdr:row>96</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>117</xdr:row>
+                <xdr:row>97</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </to>
             </anchor>
@@ -11877,24 +12562,24 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3091" r:id="rId17" name="Control 19"/>
+        <control shapeId="3086" r:id="rId18" name="Control 14"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3090" r:id="rId18" name="Control 18">
-          <controlPr defaultSize="0" r:id="rId4">
+        <control shapeId="3087" r:id="rId19" name="Control 15">
+          <controlPr defaultSize="0" r:id="rId6">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>114</xdr:row>
+                <xdr:row>98</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>115</xdr:row>
+                <xdr:row>99</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </to>
             </anchor>
@@ -11902,38 +12587,13 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3090" r:id="rId18" name="Control 18"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3089" r:id="rId19" name="Control 17">
-          <controlPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>112</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>113</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3089" r:id="rId19" name="Control 17"/>
+        <control shapeId="3087" r:id="rId19" name="Control 15"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
         <control shapeId="3088" r:id="rId20" name="Control 16">
-          <controlPr defaultSize="0" r:id="rId4">
+          <controlPr defaultSize="0" r:id="rId6">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>1</xdr:col>
@@ -11957,19 +12617,19 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3087" r:id="rId21" name="Control 15">
-          <controlPr defaultSize="0" r:id="rId4">
+        <control shapeId="3089" r:id="rId21" name="Control 17">
+          <controlPr defaultSize="0" r:id="rId6">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>98</xdr:row>
+                <xdr:row>112</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>99</xdr:row>
+                <xdr:row>113</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </to>
             </anchor>
@@ -11977,24 +12637,24 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3087" r:id="rId21" name="Control 15"/>
+        <control shapeId="3089" r:id="rId21" name="Control 17"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3086" r:id="rId22" name="Control 14">
-          <controlPr defaultSize="0" r:id="rId4">
+        <control shapeId="3090" r:id="rId22" name="Control 18">
+          <controlPr defaultSize="0" r:id="rId6">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>96</xdr:row>
+                <xdr:row>114</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>97</xdr:row>
+                <xdr:row>115</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </to>
             </anchor>
@@ -12002,24 +12662,24 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3086" r:id="rId22" name="Control 14"/>
+        <control shapeId="3090" r:id="rId22" name="Control 18"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3085" r:id="rId23" name="Control 13">
-          <controlPr defaultSize="0" r:id="rId4">
+        <control shapeId="3091" r:id="rId23" name="Control 19">
+          <controlPr defaultSize="0" r:id="rId6">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>94</xdr:row>
+                <xdr:row>116</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>95</xdr:row>
+                <xdr:row>117</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </to>
             </anchor>
@@ -12027,24 +12687,24 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3085" r:id="rId23" name="Control 13"/>
+        <control shapeId="3091" r:id="rId23" name="Control 19"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3084" r:id="rId24" name="Control 12">
-          <controlPr defaultSize="0" r:id="rId4">
+        <control shapeId="3092" r:id="rId24" name="Control 20">
+          <controlPr defaultSize="0" r:id="rId6">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>92</xdr:row>
+                <xdr:row>118</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>93</xdr:row>
+                <xdr:row>119</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </to>
             </anchor>
@@ -12052,24 +12712,24 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3084" r:id="rId24" name="Control 12"/>
+        <control shapeId="3092" r:id="rId24" name="Control 20"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3083" r:id="rId25" name="Control 11">
-          <controlPr defaultSize="0" r:id="rId4">
+        <control shapeId="3093" r:id="rId25" name="Control 21">
+          <controlPr defaultSize="0" r:id="rId6">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>61</xdr:row>
+                <xdr:row>120</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>62</xdr:row>
+                <xdr:row>121</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </to>
             </anchor>
@@ -12077,24 +12737,24 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3083" r:id="rId25" name="Control 11"/>
+        <control shapeId="3093" r:id="rId25" name="Control 21"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3082" r:id="rId26" name="Control 10">
-          <controlPr defaultSize="0" r:id="rId4">
+        <control shapeId="3094" r:id="rId26" name="Control 22">
+          <controlPr defaultSize="0" r:id="rId6">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>59</xdr:row>
+                <xdr:row>132</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>60</xdr:row>
+                <xdr:row>133</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </to>
             </anchor>
@@ -12102,24 +12762,24 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3082" r:id="rId26" name="Control 10"/>
+        <control shapeId="3094" r:id="rId26" name="Control 22"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3081" r:id="rId27" name="Control 9">
-          <controlPr defaultSize="0" r:id="rId4">
+        <control shapeId="3095" r:id="rId27" name="Control 23">
+          <controlPr defaultSize="0" r:id="rId6">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>57</xdr:row>
+                <xdr:row>134</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>58</xdr:row>
+                <xdr:row>135</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </to>
             </anchor>
@@ -12127,24 +12787,24 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3081" r:id="rId27" name="Control 9"/>
+        <control shapeId="3095" r:id="rId27" name="Control 23"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3080" r:id="rId28" name="Control 8">
-          <controlPr defaultSize="0" r:id="rId4">
+        <control shapeId="3096" r:id="rId28" name="Control 24">
+          <controlPr defaultSize="0" r:id="rId6">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>55</xdr:row>
+                <xdr:row>136</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>56</xdr:row>
+                <xdr:row>137</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </to>
             </anchor>
@@ -12152,24 +12812,24 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3080" r:id="rId28" name="Control 8"/>
+        <control shapeId="3096" r:id="rId28" name="Control 24"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3079" r:id="rId29" name="Control 7">
-          <controlPr defaultSize="0" r:id="rId4">
+        <control shapeId="3097" r:id="rId29" name="Control 25">
+          <controlPr defaultSize="0" r:id="rId6">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>53</xdr:row>
+                <xdr:row>138</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>54</xdr:row>
+                <xdr:row>139</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </to>
             </anchor>
@@ -12177,24 +12837,24 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3079" r:id="rId29" name="Control 7"/>
+        <control shapeId="3097" r:id="rId29" name="Control 25"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3078" r:id="rId30" name="Control 6">
-          <controlPr defaultSize="0" r:id="rId4">
+        <control shapeId="3098" r:id="rId30" name="Control 26">
+          <controlPr defaultSize="0" r:id="rId6">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>23</xdr:row>
+                <xdr:row>140</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>24</xdr:row>
+                <xdr:row>141</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </to>
             </anchor>
@@ -12202,24 +12862,24 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3078" r:id="rId30" name="Control 6"/>
+        <control shapeId="3098" r:id="rId30" name="Control 26"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3077" r:id="rId31" name="Control 5">
-          <controlPr defaultSize="0" r:id="rId4">
+        <control shapeId="3099" r:id="rId31" name="Control 27">
+          <controlPr defaultSize="0" r:id="rId6">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>21</xdr:row>
+                <xdr:row>142</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>22</xdr:row>
+                <xdr:row>143</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </to>
             </anchor>
@@ -12227,24 +12887,24 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3077" r:id="rId31" name="Control 5"/>
+        <control shapeId="3099" r:id="rId31" name="Control 27"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3076" r:id="rId32" name="Control 4">
-          <controlPr defaultSize="0" r:id="rId4">
+        <control shapeId="3100" r:id="rId32" name="Control 28">
+          <controlPr defaultSize="0" r:id="rId6">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>19</xdr:row>
+                <xdr:row>150</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>20</xdr:row>
+                <xdr:row>151</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </to>
             </anchor>
@@ -12252,24 +12912,24 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3076" r:id="rId32" name="Control 4"/>
+        <control shapeId="3100" r:id="rId32" name="Control 28"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3075" r:id="rId33" name="Control 3">
-          <controlPr defaultSize="0" r:id="rId4">
+        <control shapeId="3101" r:id="rId33" name="Control 29">
+          <controlPr defaultSize="0" r:id="rId6">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>17</xdr:row>
+                <xdr:row>152</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>18</xdr:row>
+                <xdr:row>153</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </to>
             </anchor>
@@ -12277,24 +12937,24 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3075" r:id="rId33" name="Control 3"/>
+        <control shapeId="3101" r:id="rId33" name="Control 29"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3074" r:id="rId34" name="Control 2">
-          <controlPr defaultSize="0" r:id="rId4">
+        <control shapeId="3102" r:id="rId34" name="Control 30">
+          <controlPr defaultSize="0" r:id="rId6">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>15</xdr:row>
+                <xdr:row>154</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>16</xdr:row>
+                <xdr:row>155</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </to>
             </anchor>
@@ -12302,24 +12962,24 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3074" r:id="rId34" name="Control 2"/>
+        <control shapeId="3102" r:id="rId34" name="Control 30"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3073" r:id="rId35" name="Control 1">
-          <controlPr defaultSize="0" r:id="rId4">
+        <control shapeId="3103" r:id="rId35" name="Control 31">
+          <controlPr defaultSize="0" r:id="rId6">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>13</xdr:row>
+                <xdr:row>156</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>14</xdr:row>
+                <xdr:row>157</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </to>
             </anchor>
@@ -12327,7 +12987,32 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3073" r:id="rId35" name="Control 1"/>
+        <control shapeId="3103" r:id="rId35" name="Control 31"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3104" r:id="rId36" name="Control 32">
+          <controlPr defaultSize="0" r:id="rId6">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>158</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>159</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3104" r:id="rId36" name="Control 32"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </controls>
